--- a/docs/architecture/evidence/authoring-format/shortstory-blank-v2.xlsx
+++ b/docs/architecture/evidence/authoring-format/shortstory-blank-v2.xlsx
@@ -3858,7 +3858,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>2026-10-19T23:31:25.674Z</t>
+    <t>2026-10-28T23:25:21.259Z</t>
   </si>
   <si>
     <t>knolstory-next</t>

--- a/docs/architecture/evidence/authoring-format/shortstory-blank-v2.xlsx
+++ b/docs/architecture/evidence/authoring-format/shortstory-blank-v2.xlsx
@@ -3858,7 +3858,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>2026-10-28T23:25:21.259Z</t>
+    <t>2026-10-30T07:24:09.391Z</t>
   </si>
   <si>
     <t>knolstory-next</t>
